--- a/Extracted_data_analysis/polar/Output-Transformed_data/summary_split_counts_question_1_3.xlsx
+++ b/Extracted_data_analysis/polar/Output-Transformed_data/summary_split_counts_question_1_3.xlsx
@@ -30,18 +30,18 @@
     <t xml:space="preserve">Percentage</t>
   </si>
   <si>
+    <t xml:space="preserve">hard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mixed</t>
+  </si>
+  <si>
     <t xml:space="preserve">soft</t>
   </si>
   <si>
-    <t xml:space="preserve">hard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mixed</t>
-  </si>
-  <si>
     <t xml:space="preserve">habit</t>
   </si>
   <si>
@@ -81,28 +81,37 @@
     <t xml:space="preserve">comm</t>
   </si>
   <si>
+    <t xml:space="preserve">single</t>
+  </si>
+  <si>
+    <t xml:space="preserve">species</t>
+  </si>
+  <si>
     <t xml:space="preserve">group</t>
   </si>
   <si>
-    <t xml:space="preserve">single</t>
-  </si>
-  <si>
-    <t xml:space="preserve">species</t>
-  </si>
-  <si>
     <t xml:space="preserve">indicators</t>
   </si>
   <si>
     <t xml:space="preserve">Abundance</t>
   </si>
   <si>
+    <t xml:space="preserve">Density</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diversity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trophic</t>
+  </si>
+  <si>
     <t xml:space="preserve">Biomass</t>
   </si>
   <si>
-    <t xml:space="preserve">Density</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diversity</t>
+    <t xml:space="preserve">Behaviour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Habitat</t>
   </si>
   <si>
     <t xml:space="preserve">Size</t>
@@ -111,21 +120,15 @@
     <t xml:space="preserve">Cover</t>
   </si>
   <si>
-    <t xml:space="preserve">Behaviour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trophic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Habitat</t>
-  </si>
-  <si>
     <t xml:space="preserve">Morphological</t>
   </si>
   <si>
     <t xml:space="preserve">taxo</t>
   </si>
   <si>
+    <t xml:space="preserve">growth</t>
+  </si>
+  <si>
     <t xml:space="preserve">geneticSequences</t>
   </si>
   <si>
@@ -135,9 +138,6 @@
     <t xml:space="preserve">Physiological</t>
   </si>
   <si>
-    <t xml:space="preserve">growth</t>
-  </si>
-  <si>
     <t xml:space="preserve">func</t>
   </si>
   <si>
@@ -147,13 +147,13 @@
     <t xml:space="preserve">collectedDataType</t>
   </si>
   <si>
+    <t xml:space="preserve">video</t>
+  </si>
+  <si>
     <t xml:space="preserve">photo</t>
   </si>
   <si>
     <t xml:space="preserve">specimen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">video</t>
   </si>
   <si>
     <t xml:space="preserve">water</t>
@@ -516,10 +516,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="3">
@@ -527,10 +527,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="4">
@@ -538,10 +538,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="5">
@@ -549,10 +549,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>19.23</v>
       </c>
     </row>
   </sheetData>
@@ -579,13 +579,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>58.62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="4">
@@ -607,7 +607,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>24.14</v>
+        <v>23.33</v>
       </c>
     </row>
   </sheetData>
@@ -637,10 +637,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>89.66</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
@@ -651,7 +651,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="4">
@@ -662,29 +662,29 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
   </sheetData>
@@ -714,10 +714,10 @@
         <v>16</v>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>96.55</v>
+        <v>96.67</v>
       </c>
     </row>
     <row r="3">
@@ -728,7 +728,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
   </sheetData>
@@ -758,10 +758,10 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>55.17</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="3">
@@ -769,10 +769,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>31.03</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -780,10 +780,10 @@
         <v>21</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>10.34</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="5">
@@ -791,10 +791,10 @@
         <v>22</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>17.24</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -824,10 +824,10 @@
         <v>24</v>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>44.83</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="3">
@@ -835,10 +835,10 @@
         <v>25</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>13.79</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="4">
@@ -846,10 +846,10 @@
         <v>26</v>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>34.48</v>
+        <v>63.33</v>
       </c>
     </row>
     <row r="5">
@@ -857,10 +857,10 @@
         <v>27</v>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.07</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="6">
@@ -871,7 +871,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>13.79</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="7">
@@ -879,10 +879,10 @@
         <v>29</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>27.59</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="8">
@@ -890,10 +890,10 @@
         <v>30</v>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>13.79</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -901,10 +901,10 @@
         <v>31</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>10.34</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="10">
@@ -912,10 +912,10 @@
         <v>32</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="11">
@@ -926,7 +926,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>24.14</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="12">
@@ -937,7 +937,7 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>10.34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -945,10 +945,10 @@
         <v>35</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>6.9</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="14">
@@ -956,10 +956,10 @@
         <v>36</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>3.45</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="15">
@@ -970,7 +970,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="16">
@@ -981,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="17">
@@ -992,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="18">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
   </sheetData>
@@ -1033,10 +1033,10 @@
         <v>42</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>41.38</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
@@ -1044,10 +1044,10 @@
         <v>43</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>34.48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -1055,10 +1055,10 @@
         <v>44</v>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>68.97</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="5">
@@ -1069,7 +1069,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>10.34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -1080,7 +1080,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>6.9</v>
+        <v>6.67</v>
       </c>
     </row>
   </sheetData>
@@ -1110,10 +1110,10 @@
         <v>48</v>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>96.55</v>
+        <v>96.67</v>
       </c>
     </row>
     <row r="3">
@@ -1124,7 +1124,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="4">
@@ -1135,7 +1135,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
   </sheetData>
